--- a/analytics/daily_stats_usr_0673194d-712d-4b5d-8167-1f03ed3233cb.xlsx
+++ b/analytics/daily_stats_usr_0673194d-712d-4b5d-8167-1f03ed3233cb.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,6 +706,45 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>40</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/04/08</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>40</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
